--- a/Stability analysis of ALNS/exps_record_all_parallelexp6062510001parallel3(3).xlsx
+++ b/Stability analysis of ALNS/exps_record_all_parallelexp6062510001parallel3(3).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="11940"/>
+    <workbookView windowWidth="27660" windowHeight="11960"/>
   </bookViews>
   <sheets>
     <sheet name="exps_record" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>exp_number</t>
   </si>
@@ -138,39 +138,6 @@
   </si>
   <si>
     <t>note</t>
-  </si>
-  <si>
-    <t>cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>vehicle_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> request_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>wait_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>transshipment_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>un_load_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>emissions_per_container_per_km</t>
-  </si>
-  <si>
-    <t>emission_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>storage_cost_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>delay_penalty_per_ton_per_km</t>
-  </si>
-  <si>
-    <t>freight_turnover(t*km)</t>
   </si>
   <si>
     <t>[0.18, 0.49]</t>
@@ -186,12 +153,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -678,19 +644,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -699,7 +665,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,7 +794,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1175,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AV9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="14" max="15" width="12.9230769230769"/>
@@ -1183,7 +1149,7 @@
     <col min="21" max="22" width="12.9230769230769"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,41 +1261,8 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="2" spans="1:48">
+    <row r="2" spans="1:37">
       <c r="A2">
         <v>6062510001</v>
       </c>
@@ -1361,7 +1294,7 @@
         <v>0.9</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -1415,10 +1348,10 @@
         <v>173.591580167413</v>
       </c>
       <c r="AC2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE2">
         <v>1</v>
@@ -1439,43 +1372,10 @@
         <v>44.4444444444444</v>
       </c>
       <c r="AK2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL2">
-        <v>1.806847597652</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>1.6740541585139</v>
-      </c>
-      <c r="AO2">
-        <v>0.000971084861221828</v>
-      </c>
-      <c r="AP2">
-        <v>0.0552697055342175</v>
-      </c>
-      <c r="AQ2">
-        <v>0.0274899147281204</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0.0101456627291833</v>
-      </c>
-      <c r="AU2">
-        <v>0.0389170712853588</v>
-      </c>
-      <c r="AV2">
-        <v>20698.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:48">
+    <row r="3" spans="1:37">
       <c r="A3">
         <v>6062510002</v>
       </c>
@@ -1507,7 +1407,7 @@
         <v>0.9</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -1561,10 +1461,10 @@
         <v>364.336180808954</v>
       </c>
       <c r="AC3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE3">
         <v>1</v>
@@ -1585,43 +1485,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="AK3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL3">
-        <v>1.22675161044245</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>1.09104449906764</v>
-      </c>
-      <c r="AO3">
-        <v>0.000758391252754704</v>
-      </c>
-      <c r="AP3">
-        <v>0.0396253602305476</v>
-      </c>
-      <c r="AQ3">
-        <v>0.0212641973215799</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0.00931301915578912</v>
-      </c>
-      <c r="AU3">
-        <v>0.064746143414138</v>
-      </c>
-      <c r="AV3">
-        <v>47192</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:48">
+    <row r="4" spans="1:37">
       <c r="A4">
         <v>6062510003</v>
       </c>
@@ -1653,7 +1520,7 @@
         <v>0.9</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1707,10 +1574,10 @@
         <v>1189.71115087252</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE4">
         <v>1</v>
@@ -1731,43 +1598,10 @@
         <v>65.3846153846154</v>
       </c>
       <c r="AK4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL4">
-        <v>1.48302433273747</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>1.35519501633483</v>
-      </c>
-      <c r="AO4">
-        <v>0.000976237440670653</v>
-      </c>
-      <c r="AP4">
-        <v>0.0326080256426062</v>
-      </c>
-      <c r="AQ4">
-        <v>0.0269062442211675</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0.0100782839178943</v>
-      </c>
-      <c r="AU4">
-        <v>0.0572605251802996</v>
-      </c>
-      <c r="AV4">
-        <v>64892</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:48">
+    <row r="5" spans="1:37">
       <c r="A5">
         <v>6062510004</v>
       </c>
@@ -1799,7 +1633,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -1853,10 +1687,10 @@
         <v>2553.01535107382</v>
       </c>
       <c r="AC5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE5">
         <v>1</v>
@@ -1877,43 +1711,10 @@
         <v>62.2222222222222</v>
       </c>
       <c r="AK5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL5">
-        <v>1.48420214121599</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>1.3021920336725</v>
-      </c>
-      <c r="AO5">
-        <v>0.000520726739134632</v>
-      </c>
-      <c r="AP5">
-        <v>0.043963469966984</v>
-      </c>
-      <c r="AQ5">
-        <v>0.0268038151873805</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0.011222559033074</v>
-      </c>
-      <c r="AU5">
-        <v>0.0994996041936169</v>
-      </c>
-      <c r="AV5">
-        <v>103586</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:48">
+    <row r="6" spans="1:37">
       <c r="A6">
         <v>6062510005</v>
       </c>
@@ -1945,7 +1746,7 @@
         <v>0.9</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1999,10 +1800,10 @@
         <v>7303.79164795531</v>
       </c>
       <c r="AC6" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD6" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE6">
         <v>1</v>
@@ -2023,43 +1824,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="AK6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL6">
-        <v>1.50914057896213</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1.25815266946001</v>
-      </c>
-      <c r="AO6">
-        <v>0.000464762802719651</v>
-      </c>
-      <c r="AP6">
-        <v>0.0262861648127903</v>
-      </c>
-      <c r="AQ6">
-        <v>0.0200803865708097</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0.00615700984715172</v>
-      </c>
-      <c r="AU6">
-        <v>0.197999609852841</v>
-      </c>
-      <c r="AV6">
-        <v>123030.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:48">
+    <row r="7" spans="1:37">
       <c r="A7">
         <v>6062510006</v>
       </c>
@@ -2091,7 +1859,7 @@
         <v>0.9</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -2145,10 +1913,10 @@
         <v>28544.6910685618</v>
       </c>
       <c r="AC7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE7">
         <v>1</v>
@@ -2169,43 +1937,10 @@
         <v>60.4166666666667</v>
       </c>
       <c r="AK7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL7">
-        <v>1.58947319508011</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>1.28817555499116</v>
-      </c>
-      <c r="AO7">
-        <v>0.000567068019136375</v>
-      </c>
-      <c r="AP7">
-        <v>0.0355204710492352</v>
-      </c>
-      <c r="AQ7">
-        <v>0.0253860188357496</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0.0116932996770866</v>
-      </c>
-      <c r="AU7">
-        <v>0.228130774732936</v>
-      </c>
-      <c r="AV7">
-        <v>385862</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:48">
+    <row r="8" spans="1:37">
       <c r="A8">
         <v>6062510007</v>
       </c>
@@ -2237,7 +1972,7 @@
         <v>0.9</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -2291,10 +2026,10 @@
         <v>91000.5099241012</v>
       </c>
       <c r="AC8" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD8" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE8">
         <v>1</v>
@@ -2315,43 +2050,10 @@
         <v>66.9014084507042</v>
       </c>
       <c r="AK8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL8">
-        <v>1.4602443641929</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>1.24812687838397</v>
-      </c>
-      <c r="AO8">
-        <v>0.000368417466415779</v>
-      </c>
-      <c r="AP8">
-        <v>0.0326355293020038</v>
-      </c>
-      <c r="AQ8">
-        <v>0.0221809171388288</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0.0113271755709187</v>
-      </c>
-      <c r="AU8">
-        <v>0.145605460744592</v>
-      </c>
-      <c r="AV8">
-        <v>763156</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:48">
+    <row r="9" spans="1:37">
       <c r="A9">
         <v>6062510008</v>
       </c>
@@ -2383,7 +2085,7 @@
         <v>0.9</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -2391,32 +2093,32 @@
       <c r="M9">
         <v>32</v>
       </c>
-      <c r="N9">
-        <v>2491945.238</v>
-      </c>
-      <c r="O9">
-        <v>2166209.33210769</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>654.38</v>
+      <c r="N9" s="2">
+        <v>2491945.368</v>
+      </c>
+      <c r="O9" s="2">
+        <v>2123857.71</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>661.56</v>
       </c>
       <c r="R9" s="2">
-        <v>39590.2271758448</v>
+        <v>40544</v>
       </c>
       <c r="S9" s="2">
-        <v>31029</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>10113.5</v>
-      </c>
-      <c r="V9">
-        <v>244348.711</v>
+        <v>30723</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>14111.945</v>
+      </c>
+      <c r="V9" s="2">
+        <v>282047.156</v>
       </c>
       <c r="W9">
         <v>51352.4642523308</v>
@@ -2437,10 +2139,10 @@
         <v>176381.619756349</v>
       </c>
       <c r="AC9" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AD9" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -2461,40 +2163,7 @@
         <v>71.0727969348659</v>
       </c>
       <c r="AK9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL9">
-        <v>-66790.132054254</v>
-      </c>
-      <c r="AM9">
-        <v>-66791.4330636295</v>
-      </c>
-      <c r="AN9">
-        <v>-66790.3409050988</v>
-      </c>
-      <c r="AO9">
-        <v>-66791.4326109773</v>
-      </c>
-      <c r="AP9">
-        <v>-66791.4076214368</v>
-      </c>
-      <c r="AQ9">
-        <v>-66791.4131905065</v>
-      </c>
-      <c r="AR9">
-        <v>-66791.4330636295</v>
-      </c>
-      <c r="AS9">
-        <v>-66791.4330636295</v>
-      </c>
-      <c r="AT9">
-        <v>-66791.4266041599</v>
-      </c>
-      <c r="AU9">
-        <v>-66791.2764401843</v>
-      </c>
-      <c r="AV9">
-        <v>1497198</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
